--- a/data/kindergarten.xlsx
+++ b/data/kindergarten.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V3 final\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,72 +19,678 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="103">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="250">
+  <x:si>
+    <x:t>경기도 시흥시 승지로 110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-8000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-7411</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행로 92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-432-0887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-315-2133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1327</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1557</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-0052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-319-4368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7013-8647</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥월곶초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-432-7979</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-3580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8085-7007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-2970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-403-4222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-7767</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-412-4390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-8518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-9001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6876</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-9419</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥도원초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-8080</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 455</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-7903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-487-2527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-499-7330</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-435-3344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한여울초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-1700~2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-495-7336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥장현초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-315-1800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-0670</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉정초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 1학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 2명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(일반 : 2명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현장곡로 37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 59-4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감초등길 49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로533번길 21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새빛유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다원유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧새봄유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧누리유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해오름유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>꿈나래유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모아유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매화유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>궁전유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해맑은유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>등밭유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이그루유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해피아이유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이레유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은행유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아름유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보람유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧초록유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진영유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빛가람유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화리라유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하하유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예일유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소망유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세종유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풍림월드유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한울유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라온초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-7096-6380</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현동 628</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 황고개로 567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로103번길 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 오이도어시장로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로7번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 44-8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 은행로12번길 24 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은계중앙로 165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대골안길 26-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은계로142번길 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 16-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 시청로 80번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 거북섬남로 80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 죽율로 45-42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 연성로29번길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 승지로 104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 인선길 56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8032-6504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-5600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7678</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧동 275</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧누리초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-2602</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-504-0101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-3210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8040-6570</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-405-3115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-4430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-0670</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7016-3070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-8039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검바위초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 검바위1로 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-499-3921</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-6100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3640</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-319-0973</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧한울초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-7890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행로 280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>병설</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로411번길 51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로375번길 19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 신현로38번길 23-1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 7-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 정왕천로427번길 13 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로408번길 19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서촌초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 3명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥터초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 9명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 6명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 1명)</x:t>
+  </x:si>
   <x:si>
     <x:t>(특수 : 7명)</x:t>
   </x:si>
   <x:si>
+    <x:t>(순회 : 1학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월포초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 5명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 3학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승지초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(순회 : 3명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 10명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
     <x:t>(일반 : 1명)</x:t>
   </x:si>
   <x:si>
-    <x:t>(특수 : 6명)</x:t>
+    <x:t>생금초등학교병설유치원</x:t>
   </x:si>
   <x:si>
     <x:t>(특수 : 2학급)</x:t>
   </x:si>
   <x:si>
-    <x:t>(특수 : 5명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 3학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 3명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(순회 : 1학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 9명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 10명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 1명)</x:t>
-  </x:si>
-  <x:si>
     <x:t>(특수 : 4명)</x:t>
   </x:si>
   <x:si>
-    <x:t>(순회 : 3명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현동 628</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 1학급)</x:t>
+    <x:t>서해초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은빛초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진말초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하중초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운흥초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화1로 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 시청로 77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡군자로 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행고길 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-1004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웃터골초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-7772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7714</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-5394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-435-2222</x:t>
   </x:si>
   <x:si>
     <x:t>031-490-8204</x:t>
@@ -93,241 +699,76 @@
     <x:t>031-362-8700</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 포도원로 96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-319-0973</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-405-3115</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-7772</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧누리초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-2602</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8085-7007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8040-6570</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-499-3921</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-0670</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-5600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 110</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검바위초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운흥초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은빛초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧동 275</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-431-8000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로375번길 19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경기도 시흥시 정왕천로427번길 13 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승지초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-0052</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7013-8647</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-487-2527</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3640</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥장현초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-5394</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-6100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-2970</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-3580</x:t>
+    <x:t>경기도 시흥시 계수로 203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화로 66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7015-4415</x:t>
   </x:si>
   <x:si>
     <x:t>031-434-2336</x:t>
   </x:si>
   <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>병설</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
+    <x:t>031-318-7337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0657</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥터로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-314-3344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2730</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금모래초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8044-4570</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 거모동 612-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현능곡로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 1로 28-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">경기도 시흥시 목감둘레로 199 </x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 목감둘레로 59-4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은계중앙로 165</x:t>
-  </x:si>
-  <x:si>
     <x:t>경기도 시흥시 배곧4로 94-15</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 은계로142번길 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 오이도어시장로 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 거북섬남로 80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현장곡로 37</x:t>
+    <x:t>경기도 시흥시 배곧5로 65-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 논곡동 270-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 목감남서로 68</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 배곧4로 44-8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로7번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 시청로 80번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧초록유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아름유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한울유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다원유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화리라유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧새봄유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빛가람유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 2명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 2명)</x:t>
+    <x:t>경기도 시흥시 대골안길 26-1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -724,7 +1165,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:J25"/>
+  <x:dimension ref="A1:J74"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="8" max="8" width="18.22265625" bestFit="1" customWidth="1"/>
@@ -732,60 +1173,60 @@
   <x:sheetData>
     <x:row r="1" spans="1:10">
       <x:c r="A1" t="s">
-        <x:v>14</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>16</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>15</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>101</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>17</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>20</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10">
       <x:c r="A2" t="s">
-        <x:v>37</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>67</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>37.432909100000003</x:v>
@@ -796,738 +1237,2306 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" t="s">
-        <x:v>91</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>68</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I3" s="1">
-        <x:v>37.342656859999998</x:v>
+        <x:v>37.453452089999999</x:v>
       </x:c>
       <x:c r="J3" s="1">
-        <x:v>126.7475565</x:v>
+        <x:v>126.8208472</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" t="s">
-        <x:v>29</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>67</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>37.382572449999998</x:v>
+        <x:v>37.55432407</x:v>
       </x:c>
       <x:c r="J4" s="1">
-        <x:v>126.7320802</x:v>
+        <x:v>127.0711714</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" t="s">
-        <x:v>98</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>69</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>37.373172269999998</x:v>
+        <x:v>37.346999019999998</x:v>
       </x:c>
       <x:c r="J5" s="1">
-        <x:v>126.7333555</x:v>
+        <x:v>126.7471808</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" t="s">
-        <x:v>97</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>69</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>37.37621867</x:v>
+        <x:v>37.441760180000003</x:v>
       </x:c>
       <x:c r="J6" s="1">
-        <x:v>126.7282302</x:v>
+        <x:v>126.7951107</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" t="s">
-        <x:v>86</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>69</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>37.360445239999997</x:v>
+        <x:v>37.380169510000002</x:v>
       </x:c>
       <x:c r="J7" s="1">
-        <x:v>126.71181230000001</x:v>
+        <x:v>126.78067129999999</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" t="s">
-        <x:v>99</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>69</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>37.380421949999999</x:v>
+        <x:v>37.357774300000003</x:v>
       </x:c>
       <x:c r="J8" s="1">
-        <x:v>126.7927463</x:v>
+        <x:v>126.735198</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" t="s">
-        <x:v>87</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>69</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>37.372840920000002</x:v>
+        <x:v>37.342656859999998</x:v>
       </x:c>
       <x:c r="J9" s="1">
-        <x:v>126.84875</x:v>
+        <x:v>126.7475565</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" t="s">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>67</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>37.375042999999998</x:v>
+        <x:v>37.442546270000001</x:v>
       </x:c>
       <x:c r="J10" s="1">
-        <x:v>126.8445569</x:v>
+        <x:v>126.7974353</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" t="s">
-        <x:v>53</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>67</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>37.443779650000003</x:v>
+        <x:v>37.415187899999999</x:v>
       </x:c>
       <x:c r="J11" s="1">
-        <x:v>126.7836499</x:v>
+        <x:v>126.8144973</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>67</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>37.360227899999998</x:v>
+        <x:v>37.372791290000002</x:v>
       </x:c>
       <x:c r="J12" s="1">
-        <x:v>126.73006460000001</x:v>
+        <x:v>126.8116675</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>67</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>37.360227899999998</x:v>
+        <x:v>37.386837419999999</x:v>
       </x:c>
       <x:c r="J13" s="1">
-        <x:v>126.73006460000001</x:v>
+        <x:v>126.8589546</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" t="s">
-        <x:v>92</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>69</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>37.320191129999998</x:v>
+        <x:v>37.383287889999998</x:v>
       </x:c>
       <x:c r="J14" s="1">
-        <x:v>126.6894542</x:v>
+        <x:v>126.73368550000001</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" t="s">
-        <x:v>94</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>68</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>37.34600373</x:v>
+        <x:v>37.382572449999998</x:v>
       </x:c>
       <x:c r="J15" s="1">
-        <x:v>126.752028</x:v>
+        <x:v>126.7320802</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" t="s">
-        <x:v>96</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>69</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>37.33953726</x:v>
+        <x:v>37.372439399999998</x:v>
       </x:c>
       <x:c r="J16" s="1">
-        <x:v>126.7516995</x:v>
+        <x:v>126.73497690000001</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" t="s">
-        <x:v>93</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>69</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>37.372028919999998</x:v>
+        <x:v>37.373172269999998</x:v>
       </x:c>
       <x:c r="J17" s="1">
-        <x:v>126.7953321</x:v>
+        <x:v>126.7333555</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" t="s">
-        <x:v>58</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>67</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>37.38182484</x:v>
+        <x:v>37.37621867</x:v>
       </x:c>
       <x:c r="J18" s="1">
-        <x:v>126.799009</x:v>
+        <x:v>126.7282302</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" t="s">
-        <x:v>88</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>68</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>37.434253689999998</x:v>
+        <x:v>37.375856390000003</x:v>
       </x:c>
       <x:c r="J19" s="1">
-        <x:v>126.7844394</x:v>
+        <x:v>126.7285906</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" t="s">
-        <x:v>38</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>67</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>37.372789429999997</x:v>
+        <x:v>37.360445239999997</x:v>
       </x:c>
       <x:c r="J20" s="1">
-        <x:v>126.85293179999999</x:v>
+        <x:v>126.71181230000001</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" t="s">
-        <x:v>90</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>69</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>37.440646219999998</x:v>
+        <x:v>37.360480109999997</x:v>
       </x:c>
       <x:c r="J21" s="1">
-        <x:v>126.80779800000001</x:v>
+        <x:v>126.7128135</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>67</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>37.434060070000001</x:v>
+        <x:v>37.360549570000003</x:v>
       </x:c>
       <x:c r="J22" s="1">
-        <x:v>126.80521040000001</x:v>
+        <x:v>126.71808919999999</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>69</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>37.376645320000002</x:v>
+        <x:v>37.343343130000001</x:v>
       </x:c>
       <x:c r="J23" s="1">
-        <x:v>126.8584295</x:v>
+        <x:v>126.7533865</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>67</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>37.378576770000002</x:v>
+        <x:v>37.380421949999999</x:v>
       </x:c>
       <x:c r="J24" s="1">
-        <x:v>126.8588956</x:v>
+        <x:v>126.7927463</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" t="s">
-        <x:v>89</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>68</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H25" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I25" s="1">
+        <x:v>37.372840920000002</x:v>
+      </x:c>
+      <x:c r="J25" s="1">
+        <x:v>126.84875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
+      <x:c r="A26" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B26" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H26" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I26" s="1">
+        <x:v>37.375042999999998</x:v>
+      </x:c>
+      <x:c r="J26" s="1">
+        <x:v>126.8445569</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
+      <x:c r="A27" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B27" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H27" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I27" s="1">
+        <x:v>37.305045300000003</x:v>
+      </x:c>
+      <x:c r="J27" s="1">
+        <x:v>126.8237615</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:10">
+      <x:c r="A28" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H28" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I28" s="1">
+        <x:v>37.350146029999998</x:v>
+      </x:c>
+      <x:c r="J28" s="1">
+        <x:v>126.75737770000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10">
+      <x:c r="A29" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H29" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I29" s="1">
+        <x:v>36.650487099999999</x:v>
+      </x:c>
+      <x:c r="J29" s="1">
+        <x:v>127.3995931</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
+      <x:c r="A30" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H30" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I30" s="1">
+        <x:v>37.356147409999998</x:v>
+      </x:c>
+      <x:c r="J30" s="1">
+        <x:v>126.72508569999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:10">
+      <x:c r="A31" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B31" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H31" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I31" s="1">
+        <x:v>37.377569469999997</x:v>
+      </x:c>
+      <x:c r="J31" s="1">
+        <x:v>126.7824507</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:10">
+      <x:c r="A32" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B32" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H32" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I32" s="1">
+        <x:v>37.443779650000003</x:v>
+      </x:c>
+      <x:c r="J32" s="1">
+        <x:v>126.7836499</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:10">
+      <x:c r="A33" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B33" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H33" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I33" s="1">
+        <x:v>37.447542069999997</x:v>
+      </x:c>
+      <x:c r="J33" s="1">
+        <x:v>126.788664</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:10">
+      <x:c r="A34" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B34" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H34" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I34" s="1">
+        <x:v>37.360227899999998</x:v>
+      </x:c>
+      <x:c r="J34" s="1">
+        <x:v>126.73006460000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:10">
+      <x:c r="A35" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B35" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H35" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I35" s="1">
+        <x:v>37.360227899999998</x:v>
+      </x:c>
+      <x:c r="J35" s="1">
+        <x:v>126.73006460000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:10">
+      <x:c r="A36" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H36" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I36" s="1">
+        <x:v>37.320191129999998</x:v>
+      </x:c>
+      <x:c r="J36" s="1">
+        <x:v>126.6894542</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:10">
+      <x:c r="A37" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H25" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I25" s="1">
+      <x:c r="E37" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H37" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I37" s="1">
+        <x:v>37.34600373</x:v>
+      </x:c>
+      <x:c r="J37" s="1">
+        <x:v>126.752028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:10">
+      <x:c r="A38" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B38" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H38" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I38" s="1">
+        <x:v>37.33953726</x:v>
+      </x:c>
+      <x:c r="J38" s="1">
+        <x:v>126.7516995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:10">
+      <x:c r="A39" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H39" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I39" s="1">
+        <x:v>37.372028919999998</x:v>
+      </x:c>
+      <x:c r="J39" s="1">
+        <x:v>126.7953321</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:10">
+      <x:c r="A40" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B40" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H40" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I40" s="1">
+        <x:v>37.373699430000002</x:v>
+      </x:c>
+      <x:c r="J40" s="1">
+        <x:v>126.7943013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:10">
+      <x:c r="A41" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B41" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H41" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I41" s="1">
+        <x:v>37.36530372</x:v>
+      </x:c>
+      <x:c r="J41" s="1">
+        <x:v>126.8127654</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:10">
+      <x:c r="A42" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H42" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I42" s="1">
+        <x:v>37.440074950000003</x:v>
+      </x:c>
+      <x:c r="J42" s="1">
+        <x:v>126.7779609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:10">
+      <x:c r="A43" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B43" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H43" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I43" s="1">
+        <x:v>37.391693740000001</x:v>
+      </x:c>
+      <x:c r="J43" s="1">
+        <x:v>126.737414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:10">
+      <x:c r="A44" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B44" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H44" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I44" s="1">
+        <x:v>37.432958540000001</x:v>
+      </x:c>
+      <x:c r="J44" s="1">
+        <x:v>126.7958409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:10">
+      <x:c r="A45" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B45" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H45" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I45" s="1">
+        <x:v>37.442580669999998</x:v>
+      </x:c>
+      <x:c r="J45" s="1">
+        <x:v>126.8007123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:10">
+      <x:c r="A46" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B46" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H46" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I46" s="1">
+        <x:v>37.38182484</x:v>
+      </x:c>
+      <x:c r="J46" s="1">
+        <x:v>126.799009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:10">
+      <x:c r="A47" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B47" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H47" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I47" s="1">
+        <x:v>33.479206240000003</x:v>
+      </x:c>
+      <x:c r="J47" s="1">
+        <x:v>126.89620720000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:10">
+      <x:c r="A48" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B48" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H48" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I48" s="1">
+        <x:v>35.278189709999999</x:v>
+      </x:c>
+      <x:c r="J48" s="1">
+        <x:v>128.8294649</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:10">
+      <x:c r="A49" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B49" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H49" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I49" s="1">
+        <x:v>37.434253689999998</x:v>
+      </x:c>
+      <x:c r="J49" s="1">
+        <x:v>126.7844394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:10">
+      <x:c r="A50" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B50" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H50" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I50" s="1">
+        <x:v>37.447135639999999</x:v>
+      </x:c>
+      <x:c r="J50" s="1">
+        <x:v>126.7890242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:10">
+      <x:c r="A51" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B51" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H51" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I51" s="1">
+        <x:v>37.413689120000001</x:v>
+      </x:c>
+      <x:c r="J51" s="1">
+        <x:v>126.814418</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:10">
+      <x:c r="A52" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B52" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H52" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I52" s="1">
+        <x:v>37.344795099999999</x:v>
+      </x:c>
+      <x:c r="J52" s="1">
+        <x:v>126.6923068</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:10">
+      <x:c r="A53" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B53" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H53" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I53" s="1">
+        <x:v>37.372789429999997</x:v>
+      </x:c>
+      <x:c r="J53" s="1">
+        <x:v>126.85293179999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:10">
+      <x:c r="A54" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B54" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H54" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I54" s="1">
+        <x:v>37.43967318</x:v>
+      </x:c>
+      <x:c r="J54" s="1">
+        <x:v>126.79916059999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:10">
+      <x:c r="A55" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B55" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H55" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I55" s="1">
+        <x:v>36.203201489999998</x:v>
+      </x:c>
+      <x:c r="J55" s="1">
+        <x:v>129.36797970000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:10">
+      <x:c r="A56" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B56" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F56" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G56" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H56" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I56" s="1">
+        <x:v>37.440646219999998</x:v>
+      </x:c>
+      <x:c r="J56" s="1">
+        <x:v>126.80779800000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:10">
+      <x:c r="A57" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B57" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G57" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H57" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I57" s="1">
+        <x:v>37.447729500000001</x:v>
+      </x:c>
+      <x:c r="J57" s="1">
+        <x:v>126.7977875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:10">
+      <x:c r="A58" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B58" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F58" s="1" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G58" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H58" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I58" s="1">
+        <x:v>37.434060070000001</x:v>
+      </x:c>
+      <x:c r="J58" s="1">
+        <x:v>126.80521040000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:10">
+      <x:c r="A59" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B59" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F59" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G59" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H59" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I59" s="1">
+        <x:v>37.430444809999997</x:v>
+      </x:c>
+      <x:c r="J59" s="1">
+        <x:v>126.79382529999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:10">
+      <x:c r="A60" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B60" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F60" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G60" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H60" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I60" s="1">
+        <x:v>37.394852880000002</x:v>
+      </x:c>
+      <x:c r="J60" s="1">
+        <x:v>126.8550556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:10">
+      <x:c r="A61" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B61" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F61" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G61" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H61" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I61" s="1">
+        <x:v>36.504739270000002</x:v>
+      </x:c>
+      <x:c r="J61" s="1">
+        <x:v>126.69270229999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:10">
+      <x:c r="A62" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B62" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E62" s="1" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F62" s="1" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G62" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H62" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I62" s="1">
+        <x:v>37.376645320000002</x:v>
+      </x:c>
+      <x:c r="J62" s="1">
+        <x:v>126.8584295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:10">
+      <x:c r="A63" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B63" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D63" s="1" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="E63" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F63" s="1" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G63" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H63" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I63" s="1">
+        <x:v>37.378576770000002</x:v>
+      </x:c>
+      <x:c r="J63" s="1">
+        <x:v>126.8588956</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:10">
+      <x:c r="A64" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B64" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="E64" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F64" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G64" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H64" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I64" s="1">
+        <x:v>37.380704809999997</x:v>
+      </x:c>
+      <x:c r="J64" s="1">
+        <x:v>126.788132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:10">
+      <x:c r="A65" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B65" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="E65" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F65" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G65" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H65" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I65" s="1">
+        <x:v>37.436064360000003</x:v>
+      </x:c>
+      <x:c r="J65" s="1">
+        <x:v>126.7783479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:10">
+      <x:c r="A66" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B66" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E66" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F66" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G66" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H66" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I66" s="1">
+        <x:v>37.390670659999998</x:v>
+      </x:c>
+      <x:c r="J66" s="1">
+        <x:v>126.7356096</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:10">
+      <x:c r="A67" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B67" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E67" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F67" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G67" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H67" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I67" s="1">
+        <x:v>37.393358499999998</x:v>
+      </x:c>
+      <x:c r="J67" s="1">
+        <x:v>126.80712990000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:10">
+      <x:c r="A68" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B68" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E68" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F68" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G68" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H68" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I68" s="1">
+        <x:v>37.393402000000002</x:v>
+      </x:c>
+      <x:c r="J68" s="1">
+        <x:v>126.8054339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:10">
+      <x:c r="A69" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B69" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E69" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F69" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G69" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H69" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I69" s="1">
+        <x:v>37.365439700000003</x:v>
+      </x:c>
+      <x:c r="J69" s="1">
+        <x:v>126.80541169999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:10">
+      <x:c r="A70" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B70" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D70" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E70" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F70" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G70" s="1" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H70" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I70" s="1">
         <x:v>37.344646590000004</x:v>
       </x:c>
-      <x:c r="J25" s="1">
+      <x:c r="J70" s="1">
         <x:v>126.6914244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:10">
+      <x:c r="A71" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B71" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="E71" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F71" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G71" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H71" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I71" s="1">
+        <x:v>37.365413429999997</x:v>
+      </x:c>
+      <x:c r="J71" s="1">
+        <x:v>126.7377314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:10">
+      <x:c r="A72" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B72" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C72" s="1" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D72" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E72" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F72" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G72" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H72" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I72" s="1">
+        <x:v>37.380904119999997</x:v>
+      </x:c>
+      <x:c r="J72" s="1">
+        <x:v>126.79892460000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:10">
+      <x:c r="A73" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B73" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C73" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E73" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F73" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G73" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H73" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I73" s="1">
+        <x:v>37.407710399999999</x:v>
+      </x:c>
+      <x:c r="J73" s="1">
+        <x:v>126.7837645</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:10">
+      <x:c r="A74" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B74" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C74" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D74" s="1" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="E74" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F74" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G74" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H74" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I74" s="1">
+        <x:v>37.439717219999999</x:v>
+      </x:c>
+      <x:c r="J74" s="1">
+        <x:v>126.7975107</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/kindergarten.xlsx
+++ b/data/kindergarten.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V3 final + 치료센터\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V3 final + 치료센터 +예체능\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -21,298 +21,298 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="98">
   <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 목감둘레로 199 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 거북섬남로 80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 44-8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현장곡로 37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 59-4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 오이도어시장로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 시청로 80번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은계로142번길 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로7번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은계중앙로 165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 94-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>병설</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 1학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(일반 : 2명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 3명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 9명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 6명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 5명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 7명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(일반 : 1명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 1명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 2명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 3학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승지초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 10명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 2학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 4명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은빛초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빛가람유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화리라유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다원유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한울유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧새봄유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아름유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧초록유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 정왕천로427번길 13 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로375번길 19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-5600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-8000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7013-8647</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-363-1700</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 승지로 110</x:t>
   </x:si>
   <x:si>
-    <x:t>031-431-8000</x:t>
-  </x:si>
-  <x:si>
     <x:t>031-433-0052</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7013-8647</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧4로 44-8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 59-4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현장곡로 37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로7번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 1학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 2명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 2명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 3명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 9명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 1명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 5명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 3학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 7명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 6명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 1명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 2학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 10명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 4명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승지초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은빛초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다원유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧새봄유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한울유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧초록유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아름유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빛가람유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화리라유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화유치원</x:t>
-  </x:si>
-  <x:si>
     <x:t>일반학급 배치 학생 수</x:t>
   </x:si>
   <x:si>
+    <x:t>배곧누리초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-0670</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검바위초등학교병설유치원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-499-3921</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-6100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8040-6570</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-2602</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 배곧동 275</x:t>
   </x:si>
   <x:si>
-    <x:t>배곧누리초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-5600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-0670</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검바위초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-499-3921</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-6100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8040-6570</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-2602</x:t>
+    <x:t>031-8085-7007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-490-8204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-319-0973</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-405-3115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-8700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-3580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-2970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-487-2527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-7772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현동 628</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-2336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 96</x:t>
   </x:si>
   <x:si>
     <x:t>031-364-3640</x:t>
   </x:si>
   <x:si>
-    <x:t>031-319-0973</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-405-3115</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경기도 시흥시 정왕천로427번길 13 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로375번길 19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 오이도어시장로 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은계중앙로 165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-3580</x:t>
-  </x:si>
-  <x:si>
     <x:t>특수/순회학급 배치 학생 수</x:t>
   </x:si>
   <x:si>
-    <x:t>031-8085-7007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-2970</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-487-2527</x:t>
-  </x:si>
-  <x:si>
     <x:t>시흥장현초등학교병설유치원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현동 628</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>병설</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-7772</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-490-8204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-8700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-2336</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은계로142번길 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧4로 94-15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감남서로 68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 시청로 80번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경기도 시흥시 목감둘레로 199 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 거북섬남로 80</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -717,60 +717,60 @@
   <x:sheetData>
     <x:row r="1" spans="1:10">
       <x:c r="A1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>82</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>32</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>73</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10">
       <x:c r="A2" t="s">
-        <x:v>54</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>37.432909100000003</x:v>
@@ -781,28 +781,28 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" t="s">
-        <x:v>34</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>85</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>37.342656859999998</x:v>
@@ -813,28 +813,28 @@
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" t="s">
-        <x:v>51</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>37.382572449999998</x:v>
@@ -845,28 +845,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B5" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>37.373172269999998</x:v>
@@ -877,28 +877,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>37.37621867</x:v>
@@ -909,28 +909,28 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" t="s">
-        <x:v>37</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>37.360445239999997</x:v>
@@ -941,28 +941,28 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>37.380421949999999</x:v>
@@ -973,28 +973,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>37.372840920000002</x:v>
@@ -1005,28 +1005,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>37.375042999999998</x:v>
@@ -1037,28 +1037,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>37.443779650000003</x:v>
@@ -1069,28 +1069,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>37.360227899999998</x:v>
@@ -1101,60 +1101,60 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>37.360227899999998</x:v>
+        <x:v>37.372313548133</x:v>
       </x:c>
       <x:c r="J13" s="1">
-        <x:v>126.73006460000001</x:v>
+        <x:v>126.81267577472801</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" t="s">
-        <x:v>40</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>37.320191129999998</x:v>
@@ -1165,28 +1165,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>85</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>37.34600373</x:v>
@@ -1197,28 +1197,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>37.33953726</x:v>
@@ -1229,28 +1229,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>37.372028919999998</x:v>
@@ -1261,28 +1261,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" t="s">
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B18" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>37.38182484</x:v>
@@ -1293,28 +1293,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" t="s">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>85</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>37.434253689999998</x:v>
@@ -1325,28 +1325,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>37.440646219999998</x:v>
@@ -1357,28 +1357,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>37.434060070000001</x:v>
@@ -1389,28 +1389,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" t="s">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>37.376645320000002</x:v>
@@ -1421,28 +1421,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B23" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B23" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>37.378576770000002</x:v>
@@ -1453,28 +1453,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>85</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>37.344646590000004</x:v>

--- a/data/kindergarten.xlsx
+++ b/data/kindergarten.xlsx
@@ -302,28 +302,28 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1196,45 +1196,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:K24"/>
+  <x:dimension ref="A1:J24"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
+    <x:col min="1" max="1" width="24.25390625" customWidth="1"/>
+    <x:col min="5" max="5" width="15.69140625" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="18.22265625" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:10">
       <x:c r="A1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="J1" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:11" ht="47.75">
+    <x:row r="2" spans="1:10" ht="47.75">
       <x:c r="A2" s="2" t="s">
         <x:v>8</x:v>
       </x:c>
@@ -1261,15 +1263,14 @@
       <x:c r="H2" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I2" s="5"/>
+      <x:c r="I2" s="5">
+        <x:v>37.432909100000003</x:v>
+      </x:c>
       <x:c r="J2" s="5">
-        <x:v>37.432909100000003</x:v>
-      </x:c>
-      <x:c r="K2" s="5">
         <x:v>126.7984352</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="3" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A3" s="2" t="s">
         <x:v>71</x:v>
       </x:c>
@@ -1297,15 +1298,14 @@
       <x:c r="H3" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I3" s="5"/>
+      <x:c r="I3" s="5">
+        <x:v>37.342656864938</x:v>
+      </x:c>
       <x:c r="J3" s="5">
-        <x:v>37.342656864938</x:v>
-      </x:c>
-      <x:c r="K3" s="5">
         <x:v>126.747556528698</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="4" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A4" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1333,15 +1333,14 @@
       <x:c r="H4" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I4" s="5"/>
+      <x:c r="I4" s="5">
+        <x:v>37.382572453238701</x:v>
+      </x:c>
       <x:c r="J4" s="5">
-        <x:v>37.382572453238701</x:v>
-      </x:c>
-      <x:c r="K4" s="5">
         <x:v>126.732080201381</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="5" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A5" s="2" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -1369,15 +1368,14 @@
       <x:c r="H5" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I5" s="5"/>
+      <x:c r="I5" s="5">
+        <x:v>37.373172267927401</x:v>
+      </x:c>
       <x:c r="J5" s="5">
-        <x:v>37.373172267927401</x:v>
-      </x:c>
-      <x:c r="K5" s="5">
         <x:v>126.73335552210899</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="6" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A6" s="2" t="s">
         <x:v>68</x:v>
       </x:c>
@@ -1405,15 +1403,14 @@
       <x:c r="H6" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I6" s="5"/>
+      <x:c r="I6" s="5">
+        <x:v>37.376218672493998</x:v>
+      </x:c>
       <x:c r="J6" s="5">
-        <x:v>37.376218672493998</x:v>
-      </x:c>
-      <x:c r="K6" s="5">
         <x:v>126.728230224013</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="7" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A7" s="2" t="s">
         <x:v>55</x:v>
       </x:c>
@@ -1441,15 +1438,14 @@
       <x:c r="H7" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I7" s="5"/>
+      <x:c r="I7" s="5">
+        <x:v>37.360445237683699</x:v>
+      </x:c>
       <x:c r="J7" s="5">
-        <x:v>37.360445237683699</x:v>
-      </x:c>
-      <x:c r="K7" s="5">
         <x:v>126.711812347267</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="8" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A8" s="2" t="s">
         <x:v>51</x:v>
       </x:c>
@@ -1477,15 +1473,14 @@
       <x:c r="H8" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I8" s="5"/>
+      <x:c r="I8" s="5">
+        <x:v>37.380421952033402</x:v>
+      </x:c>
       <x:c r="J8" s="5">
-        <x:v>37.380421952033402</x:v>
-      </x:c>
-      <x:c r="K8" s="5">
         <x:v>126.79274625225</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="9" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A9" s="2" t="s">
         <x:v>53</x:v>
       </x:c>
@@ -1513,15 +1508,14 @@
       <x:c r="H9" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I9" s="5"/>
+      <x:c r="I9" s="5">
+        <x:v>37.372840923077199</x:v>
+      </x:c>
       <x:c r="J9" s="5">
-        <x:v>37.372840923077199</x:v>
-      </x:c>
-      <x:c r="K9" s="5">
         <x:v>126.848749992276</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="10" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A10" s="2" t="s">
         <x:v>33</x:v>
       </x:c>
@@ -1549,15 +1543,14 @@
       <x:c r="H10" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I10" s="5"/>
+      <x:c r="I10" s="5">
+        <x:v>37.375042996582302</x:v>
+      </x:c>
       <x:c r="J10" s="5">
-        <x:v>37.375042996582302</x:v>
-      </x:c>
-      <x:c r="K10" s="5">
         <x:v>126.84455691981201</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="11" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A11" s="2" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -1585,15 +1578,14 @@
       <x:c r="H11" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I11" s="5"/>
+      <x:c r="I11" s="5">
+        <x:v>37.443779653554003</x:v>
+      </x:c>
       <x:c r="J11" s="5">
-        <x:v>37.443779653554003</x:v>
-      </x:c>
-      <x:c r="K11" s="5">
         <x:v>126.783649896252</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="12" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A12" s="2" t="s">
         <x:v>31</x:v>
       </x:c>
@@ -1621,15 +1613,14 @@
       <x:c r="H12" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I12" s="5"/>
+      <x:c r="I12" s="5">
+        <x:v>37.3602279025339</x:v>
+      </x:c>
       <x:c r="J12" s="5">
-        <x:v>37.3602279025339</x:v>
-      </x:c>
-      <x:c r="K12" s="5">
         <x:v>126.730064615743</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="13" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A13" s="2" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -1657,15 +1648,14 @@
       <x:c r="H13" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I13" s="5"/>
+      <x:c r="I13" s="5">
+        <x:v>37.372313548133</x:v>
+      </x:c>
       <x:c r="J13" s="5">
-        <x:v>37.372313548133</x:v>
-      </x:c>
-      <x:c r="K13" s="5">
         <x:v>126.81267577472801</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="14" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A14" s="2" t="s">
         <x:v>74</x:v>
       </x:c>
@@ -1693,15 +1683,14 @@
       <x:c r="H14" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I14" s="5"/>
+      <x:c r="I14" s="5">
+        <x:v>37.320191134449601</x:v>
+      </x:c>
       <x:c r="J14" s="5">
-        <x:v>37.320191134449601</x:v>
-      </x:c>
-      <x:c r="K14" s="5">
         <x:v>126.68945416858701</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="15" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A15" s="2" t="s">
         <x:v>50</x:v>
       </x:c>
@@ -1729,15 +1718,14 @@
       <x:c r="H15" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I15" s="5"/>
+      <x:c r="I15" s="5">
+        <x:v>37.346003728298498</x:v>
+      </x:c>
       <x:c r="J15" s="5">
-        <x:v>37.346003728298498</x:v>
-      </x:c>
-      <x:c r="K15" s="5">
         <x:v>126.752028043069</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="16" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A16" s="2" t="s">
         <x:v>70</x:v>
       </x:c>
@@ -1765,15 +1753,14 @@
       <x:c r="H16" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I16" s="5"/>
+      <x:c r="I16" s="5">
+        <x:v>37.339537262968399</x:v>
+      </x:c>
       <x:c r="J16" s="5">
-        <x:v>37.339537262968399</x:v>
-      </x:c>
-      <x:c r="K16" s="5">
         <x:v>126.751699474945</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="17" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A17" s="2" t="s">
         <x:v>72</x:v>
       </x:c>
@@ -1801,15 +1788,14 @@
       <x:c r="H17" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I17" s="5"/>
+      <x:c r="I17" s="5">
+        <x:v>37.372028916235799</x:v>
+      </x:c>
       <x:c r="J17" s="5">
-        <x:v>37.372028916235799</x:v>
-      </x:c>
-      <x:c r="K17" s="5">
         <x:v>126.795332107449</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="18" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A18" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
@@ -1837,15 +1823,14 @@
       <x:c r="H18" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I18" s="5"/>
+      <x:c r="I18" s="5">
+        <x:v>37.381824841712003</x:v>
+      </x:c>
       <x:c r="J18" s="5">
-        <x:v>37.381824841712003</x:v>
-      </x:c>
-      <x:c r="K18" s="5">
         <x:v>126.799008992304</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="19" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A19" s="2" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -1873,15 +1858,14 @@
       <x:c r="H19" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I19" s="5"/>
+      <x:c r="I19" s="5">
+        <x:v>37.434253686463997</x:v>
+      </x:c>
       <x:c r="J19" s="5">
-        <x:v>37.434253686463997</x:v>
-      </x:c>
-      <x:c r="K19" s="5">
         <x:v>126.78443943865901</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="20" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A20" s="2" t="s">
         <x:v>29</x:v>
       </x:c>
@@ -1909,15 +1893,14 @@
       <x:c r="H20" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="I20" s="5"/>
+      <x:c r="I20" s="5">
+        <x:v>37.372789432445998</x:v>
+      </x:c>
       <x:c r="J20" s="5">
-        <x:v>37.372789432445998</x:v>
-      </x:c>
-      <x:c r="K20" s="5">
         <x:v>126.852931847646</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="21" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A21" s="2" t="s">
         <x:v>52</x:v>
       </x:c>
@@ -1945,15 +1928,14 @@
       <x:c r="H21" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I21" s="5"/>
+      <x:c r="I21" s="5">
+        <x:v>37.440646217015903</x:v>
+      </x:c>
       <x:c r="J21" s="5">
-        <x:v>37.440646217015903</x:v>
-      </x:c>
-      <x:c r="K21" s="5">
         <x:v>126.807797988384</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="22" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A22" s="2" t="s">
         <x:v>30</x:v>
       </x:c>
@@ -1981,15 +1963,14 @@
       <x:c r="H22" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I22" s="5"/>
+      <x:c r="I22" s="5">
+        <x:v>37.434060071312899</x:v>
+      </x:c>
       <x:c r="J22" s="5">
-        <x:v>37.434060071312899</x:v>
-      </x:c>
-      <x:c r="K22" s="5">
         <x:v>126.805210407465</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:11" ht="35.79999999999999715783">
+    <x:row r="23" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A23" s="2" t="s">
         <x:v>69</x:v>
       </x:c>
@@ -2017,15 +1998,14 @@
       <x:c r="H23" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I23" s="5"/>
+      <x:c r="I23" s="5">
+        <x:v>37.376645317668597</x:v>
+      </x:c>
       <x:c r="J23" s="5">
-        <x:v>37.376645317668597</x:v>
-      </x:c>
-      <x:c r="K23" s="5">
         <x:v>126.858429521128</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:11" ht="39.54999999999999715783">
+    <x:row r="24" spans="1:10" ht="35.79999999999999715783">
       <x:c r="A24" s="2" t="s">
         <x:v>35</x:v>
       </x:c>
@@ -2053,11 +2033,10 @@
       <x:c r="H24" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I24" s="5"/>
+      <x:c r="I24" s="5">
+        <x:v>37.3785767693022</x:v>
+      </x:c>
       <x:c r="J24" s="5">
-        <x:v>37.3785767693022</x:v>
-      </x:c>
-      <x:c r="K24" s="5">
         <x:v>126.85889558366701</x:v>
       </x:c>
     </x:row>
